--- a/splitting_sample/larger_sample/Participant_characteristics.xlsx
+++ b/splitting_sample/larger_sample/Participant_characteristics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tempu\Arousal-Project\splitting_sample\larger_sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7BED20-91F8-476E-B5E3-81BE06FB7DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAB85D0-A222-4B9E-83AB-1C39FFF33570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="187">
   <si>
     <t>SubID</t>
   </si>
@@ -595,6 +595,30 @@
   </si>
   <si>
     <t>is_group</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>count_sleepy</t>
+  </si>
+  <si>
+    <t>count_awake</t>
+  </si>
+  <si>
+    <t>is_sleepy</t>
+  </si>
+  <si>
+    <t>perc_F</t>
+  </si>
+  <si>
+    <t>num_F</t>
+  </si>
+  <si>
+    <t>awake_subj</t>
+  </si>
+  <si>
+    <t>PM01</t>
   </si>
 </sst>
 </file>
@@ -721,27 +745,7 @@
     </border>
     <border>
       <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -753,6 +757,26 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -779,17 +803,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,10 +1094,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:R132"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.26953125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.1796875" style="2" bestFit="1" customWidth="1"/>
@@ -1082,58 +1106,66 @@
     <col min="7" max="7" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.7265625" style="2"/>
+    <col min="10" max="10" width="8" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" style="9"/>
+    <col min="12" max="12" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7265625" style="10"/>
+    <col min="19" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="15" customFormat="1" ht="16" thickBot="1">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
+    <row r="1" spans="1:18" s="14" customFormat="1" ht="16" thickBot="1">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="L1" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="15" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="14" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.5">
-      <c r="A2" s="20" t="s">
+      <c r="R1" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.5">
+      <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1158,36 +1190,43 @@
         <v>14</v>
       </c>
       <c r="I2" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A2)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A2)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
+        <f>COUNTIF($L$2:$L$18, A2)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A2)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="b">
+        <f>COUNTIF($R:$R, A2)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
         <v>40</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="M2" s="9">
+      <c r="N2" s="9">
         <f>AVERAGEIF(I:I, TRUE, C:C)</f>
-        <v>23.117647058823529</v>
-      </c>
-      <c r="N2" t="s">
+        <v>23.5</v>
+      </c>
+      <c r="O2" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="P2" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="20">
         <f>AVERAGEIF(J2:J1000, TRUE, C2:C1000)</f>
         <v>23.627659574468087</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15.5">
-      <c r="A3" s="20" t="s">
+      <c r="R2" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15.5">
+      <c r="A3" s="17" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1212,36 +1251,43 @@
         <v>14</v>
       </c>
       <c r="I3" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A3)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A3)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
+        <f>COUNTIF($L$2:$L$18, A3)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A3)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="9" t="b">
+        <f>COUNTIF($R:$R, A3)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="M3" s="9" cm="1">
-        <f t="array" ref="M3">_xlfn.STDEV.S(_xlfn._xlws.FILTER(C2:C500, I2:I500=TRUE))</f>
-        <v>3.1000474379672114</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="N3" s="9" cm="1">
+        <f t="array" ref="N3">_xlfn.STDEV.S(_xlfn._xlws.FILTER(C2:C500, I2:I500=TRUE))</f>
+        <v>3.4170851011110761</v>
+      </c>
+      <c r="O3" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="P3" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="P3" s="9" cm="1">
-        <f t="array" ref="P3">_xlfn.STDEV.S(_xlfn._xlws.FILTER(C2:C500, J2:J500=TRUE))</f>
+      <c r="Q3" s="20" cm="1">
+        <f t="array" ref="Q3">_xlfn.STDEV.S(_xlfn._xlws.FILTER(C2:C500, J2:J500=TRUE))</f>
         <v>3.6982531259960552</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="15.5">
-      <c r="A4" s="20" t="s">
+      <c r="R3" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.5">
+      <c r="A4" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1266,200 +1312,286 @@
         <v>14</v>
       </c>
       <c r="I4" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A4)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A4)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
+        <f>COUNTIF($L$2:$L$18, A4)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A4)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="9" t="b">
+        <f>COUNTIF($R:$R, A4)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>59</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="M4" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="N4" s="9">
+        <f>COUNTIF(I:I, TRUE)</f>
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>146</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15.5">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="2" t="b">
+        <f>COUNTIF($L$2:$L$18, A5)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A5)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="b">
+        <f>COUNTIF($R:$R, A5)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="N5" s="9">
+        <f>COUNTIF(I:I, TRUE)</f>
+        <v>18</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q5" s="20">
+        <f>Q4 - Q6</f>
+        <v>52</v>
+      </c>
+      <c r="R5" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15.5">
+      <c r="A6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2" t="b">
+        <f>COUNTIF($L$2:$L$18, A6)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A6)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="9" t="b">
+        <f>COUNTIF($R:$R, A6)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="N6" s="9">
+        <f>COUNTIF(I:I, TRUE)</f>
+        <v>18</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q6" s="20">
+        <f>COUNTIF(J:J, TRUE)</f>
+        <v>94</v>
+      </c>
+      <c r="R6" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15.5">
+      <c r="A7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="2" t="b">
+        <f>COUNTIF($L$2:$L$18, A7)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A7)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K7" s="9" t="b">
+        <f>COUNTIF($R:$R, A7)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="N7" s="9">
+        <f>N8 / N4</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q7" s="20">
+        <f>Q8/Q4</f>
+        <v>0.33561643835616439</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.5">
+      <c r="A8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="2" t="b">
+        <f>COUNTIF($L$2:$L$18, A8)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A8)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="b">
+        <f>COUNTIF($R:$R, A8)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="M4" s="12">
+      <c r="N8" s="12">
         <f>COUNTIFS(I:I, TRUE, B:B, "F")</f>
-        <v>9</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="P4" s="12">
+        <v>10</v>
+      </c>
+      <c r="O8" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q8" s="21">
         <f>COUNTIFS(J:J, TRUE, B:B, "F")</f>
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="15.5">
-      <c r="A5" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A5)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A5)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5"/>
-      <c r="N5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.5">
-      <c r="A6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A6)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A6)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6"/>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.5">
-      <c r="A7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A7)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A7)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7"/>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15.5">
-      <c r="A8" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A8)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A8)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L8"/>
-      <c r="N8" t="s">
+      <c r="R8" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.5">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:18" ht="15.5">
+      <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1484,23 +1616,30 @@
         <v>14</v>
       </c>
       <c r="I9" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A9)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A9)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
+        <f>COUNTIF($L$2:$L$18, A9)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A9)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="9" t="b">
+        <f>COUNTIF($R:$R, A9)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
         <v>93</v>
       </c>
-      <c r="L9"/>
-      <c r="N9" t="s">
+      <c r="M9"/>
+      <c r="O9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.5">
-      <c r="A10" s="20" t="s">
+      <c r="R9" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.5">
+      <c r="A10" s="17" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1525,23 +1664,30 @@
         <v>14</v>
       </c>
       <c r="I10" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A10)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A10)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
+        <f>COUNTIF($L$2:$L$18, A10)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A10)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="9" t="b">
+        <f>COUNTIF($R:$R, A10)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
         <v>100</v>
       </c>
-      <c r="L10"/>
-      <c r="N10" t="s">
+      <c r="M10"/>
+      <c r="O10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.5">
-      <c r="A11" s="20" t="s">
+      <c r="R10" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.5">
+      <c r="A11" s="17" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1566,23 +1712,34 @@
         <v>14</v>
       </c>
       <c r="I11" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A11)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A11)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
+        <f>COUNTIF($L$2:$L$18, A11)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A11)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K11" s="9" t="b">
+        <f>COUNTIF($R:$R, A11)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
         <v>101</v>
       </c>
-      <c r="L11"/>
-      <c r="N11" t="s">
+      <c r="M11"/>
+      <c r="O11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.5">
-      <c r="A12" s="20" t="s">
+      <c r="P11" s="2">
+        <f>(23.1176 * 17 + 30) / 18</f>
+        <v>23.499955555555555</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.5">
+      <c r="A12" s="17" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1607,23 +1764,30 @@
         <v>14</v>
       </c>
       <c r="I12" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A12)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A12)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
+        <f>COUNTIF($L$2:$L$18, A12)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A12)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="9" t="b">
+        <f>COUNTIF($R:$R, A12)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
         <v>107</v>
       </c>
-      <c r="L12"/>
-      <c r="N12" t="s">
+      <c r="M12"/>
+      <c r="O12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.5">
-      <c r="A13" s="20" t="s">
+      <c r="R12" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15.5">
+      <c r="A13" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1648,23 +1812,30 @@
         <v>14</v>
       </c>
       <c r="I13" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A13)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A13)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
+        <f>COUNTIF($L$2:$L$18, A13)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A13)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="9" t="b">
+        <f>COUNTIF($R:$R, A13)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
         <v>111</v>
       </c>
-      <c r="L13"/>
-      <c r="N13" t="s">
+      <c r="M13"/>
+      <c r="O13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.5">
-      <c r="A14" s="20" t="s">
+      <c r="R13" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15.5">
+      <c r="A14" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1689,23 +1860,30 @@
         <v>14</v>
       </c>
       <c r="I14" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A14)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A14)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
+        <f>COUNTIF($L$2:$L$18, A14)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A14)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="9" t="b">
+        <f>COUNTIF($R:$R, A14)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
         <v>116</v>
       </c>
-      <c r="L14"/>
-      <c r="N14" t="s">
+      <c r="M14"/>
+      <c r="O14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="15.5">
-      <c r="A15" s="20" t="s">
+      <c r="R14" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.5">
+      <c r="A15" s="17" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1730,23 +1908,30 @@
         <v>14</v>
       </c>
       <c r="I15" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A15)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A15)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K15" t="s">
+        <f>COUNTIF($L$2:$L$18, A15)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A15)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="b">
+        <f>COUNTIF($R:$R, A15)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
         <v>121</v>
       </c>
-      <c r="L15"/>
-      <c r="N15" t="s">
+      <c r="M15"/>
+      <c r="O15" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.5">
-      <c r="A16" s="20" t="s">
+      <c r="R15" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15.5">
+      <c r="A16" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1771,23 +1956,30 @@
         <v>14</v>
       </c>
       <c r="I16" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A16)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A16)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
+        <f>COUNTIF($L$2:$L$18, A16)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A16)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="b">
+        <f>COUNTIF($R:$R, A16)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
         <v>162</v>
       </c>
-      <c r="L16"/>
-      <c r="N16" t="s">
+      <c r="M16"/>
+      <c r="O16" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.5">
-      <c r="A17" s="20" t="s">
+      <c r="R16" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15.5">
+      <c r="A17" s="17" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1812,23 +2004,30 @@
         <v>14</v>
       </c>
       <c r="I17" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A17)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A17)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
+        <f>COUNTIF($L$2:$L$18, A17)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A17)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="9" t="b">
+        <f>COUNTIF($R:$R, A17)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
         <v>166</v>
       </c>
-      <c r="L17"/>
-      <c r="N17" t="s">
+      <c r="M17"/>
+      <c r="O17" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15.5">
-      <c r="A18" s="20" t="s">
+      <c r="R17" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15.5">
+      <c r="A18" s="17" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1853,23 +2052,30 @@
         <v>14</v>
       </c>
       <c r="I18" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A18)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A18)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="K18" t="s">
+        <f>COUNTIF($L$2:$L$18, A18)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A18)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="9" t="b">
+        <f>COUNTIF($R:$R, A18)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
         <v>168</v>
       </c>
-      <c r="L18"/>
-      <c r="N18" t="s">
+      <c r="M18"/>
+      <c r="O18" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15.5">
-      <c r="A19" s="20" t="s">
+      <c r="R18" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15.5">
+      <c r="A19" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1894,19 +2100,29 @@
         <v>14</v>
       </c>
       <c r="I19" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A19)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A19)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N19" t="s">
+        <f>COUNTIF($L$2:$L$18, A19)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A19)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="9" t="b">
+        <f>COUNTIF($R:$R, A19)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>186</v>
+      </c>
+      <c r="O19" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.5">
-      <c r="A20" s="20" t="s">
+      <c r="R19" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15.5">
+      <c r="A20" s="17" t="s">
         <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1931,19 +2147,26 @@
         <v>14</v>
       </c>
       <c r="I20" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A20)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A20)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N20" t="s">
+        <f>COUNTIF($L$2:$L$18, A20)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A20)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K20" s="9" t="b">
+        <f>COUNTIF($R:$R, A20)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O20" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.5">
-      <c r="A21" s="20" t="s">
+      <c r="R20" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15.5">
+      <c r="A21" s="17" t="s">
         <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1968,19 +2191,26 @@
         <v>14</v>
       </c>
       <c r="I21" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A21)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A21)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
+        <f>COUNTIF($L$2:$L$18, A21)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A21)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="b">
+        <f>COUNTIF($R:$R, A21)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.5">
-      <c r="A22" s="20" t="s">
+      <c r="R21" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15.5">
+      <c r="A22" s="17" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -2005,19 +2235,26 @@
         <v>14</v>
       </c>
       <c r="I22" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A22)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A22)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
+        <f>COUNTIF($L$2:$L$18, A22)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A22)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="b">
+        <f>COUNTIF($R:$R, A22)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.5">
-      <c r="A23" s="20" t="s">
+      <c r="R22" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15.5">
+      <c r="A23" s="17" t="s">
         <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2042,19 +2279,26 @@
         <v>14</v>
       </c>
       <c r="I23" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A23)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A23)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
+        <f>COUNTIF($L$2:$L$18, A23)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A23)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="9" t="b">
+        <f>COUNTIF($R:$R, A23)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.5">
-      <c r="A24" s="20" t="s">
+      <c r="R23" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15.5">
+      <c r="A24" s="17" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -2079,19 +2323,26 @@
         <v>14</v>
       </c>
       <c r="I24" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A24)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A24)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
+        <f>COUNTIF($L$2:$L$18, A24)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A24)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="b">
+        <f>COUNTIF($R:$R, A24)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.5">
-      <c r="A25" s="20" t="s">
+      <c r="R24" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15.5">
+      <c r="A25" s="17" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2116,19 +2367,26 @@
         <v>14</v>
       </c>
       <c r="I25" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A25)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A25)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
+        <f>COUNTIF($L$2:$L$18, A25)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A25)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="9" t="b">
+        <f>COUNTIF($R:$R, A25)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="15.5">
-      <c r="A26" s="20" t="s">
+      <c r="R25" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15.5">
+      <c r="A26" s="17" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2153,19 +2411,26 @@
         <v>14</v>
       </c>
       <c r="I26" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A26)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A26)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
+        <f>COUNTIF($L$2:$L$18, A26)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A26)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="9" t="b">
+        <f>COUNTIF($R:$R, A26)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.5">
-      <c r="A27" s="20" t="s">
+      <c r="R26" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15.5">
+      <c r="A27" s="17" t="s">
         <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2190,19 +2455,26 @@
         <v>14</v>
       </c>
       <c r="I27" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A27)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J27" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A27)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N27" t="s">
+        <f>COUNTIF($L$2:$L$18, A27)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A27)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K27" s="9" t="b">
+        <f>COUNTIF($R:$R, A27)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.5">
-      <c r="A28" s="20" t="s">
+      <c r="R27" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15.5">
+      <c r="A28" s="17" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2227,19 +2499,26 @@
         <v>14</v>
       </c>
       <c r="I28" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A28)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A28)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N28" t="s">
+        <f>COUNTIF($L$2:$L$18, A28)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A28)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K28" s="9" t="b">
+        <f>COUNTIF($R:$R, A28)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15.5">
-      <c r="A29" s="20" t="s">
+      <c r="R28" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15.5">
+      <c r="A29" s="17" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2264,19 +2543,26 @@
         <v>14</v>
       </c>
       <c r="I29" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A29)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A29)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
+        <f>COUNTIF($L$2:$L$18, A29)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A29)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="9" t="b">
+        <f>COUNTIF($R:$R, A29)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15.5">
-      <c r="A30" s="20" t="s">
+      <c r="R29" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15.5">
+      <c r="A30" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2301,19 +2587,26 @@
         <v>14</v>
       </c>
       <c r="I30" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A30)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A30)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N30" t="s">
+        <f>COUNTIF($L$2:$L$18, A30)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A30)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K30" s="9" t="b">
+        <f>COUNTIF($R:$R, A30)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.5">
-      <c r="A31" s="20" t="s">
+      <c r="R30" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15.5">
+      <c r="A31" s="17" t="s">
         <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2338,19 +2631,26 @@
         <v>14</v>
       </c>
       <c r="I31" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A31)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A31)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N31" t="s">
+        <f>COUNTIF($L$2:$L$18, A31)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A31)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K31" s="9" t="b">
+        <f>COUNTIF($R:$R, A31)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15.5">
-      <c r="A32" s="21" t="s">
+      <c r="R31" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.5">
+      <c r="A32" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2375,19 +2675,26 @@
         <v>14</v>
       </c>
       <c r="I32" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A32)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A32)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
+        <f>COUNTIF($L$2:$L$18, A32)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A32)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="9" t="b">
+        <f>COUNTIF($R:$R, A32)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="15.5">
-      <c r="A33" s="20" t="s">
+      <c r="R32" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15.5">
+      <c r="A33" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2412,19 +2719,26 @@
         <v>14</v>
       </c>
       <c r="I33" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A33)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J33" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A33)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N33" t="s">
+        <f>COUNTIF($L$2:$L$18, A33)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J33" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A33)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K33" s="9" t="b">
+        <f>COUNTIF($R:$R, A33)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O33" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="15.5">
-      <c r="A34" s="20" t="s">
+      <c r="R33" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="15.5">
+      <c r="A34" s="17" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2449,19 +2763,26 @@
         <v>14</v>
       </c>
       <c r="I34" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A34)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A34)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
+        <f>COUNTIF($L$2:$L$18, A34)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A34)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K34" s="9" t="b">
+        <f>COUNTIF($R:$R, A34)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O34" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="15.5">
-      <c r="A35" s="20" t="s">
+      <c r="R34" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15.5">
+      <c r="A35" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2486,19 +2807,26 @@
         <v>14</v>
       </c>
       <c r="I35" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A35)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A35)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N35" t="s">
+        <f>COUNTIF($L$2:$L$18, A35)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A35)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K35" s="9" t="b">
+        <f>COUNTIF($R:$R, A35)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="15.5">
-      <c r="A36" s="20" t="s">
+      <c r="R35" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="15.5">
+      <c r="A36" s="17" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2523,19 +2851,26 @@
         <v>14</v>
       </c>
       <c r="I36" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A36)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A36)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
+        <f>COUNTIF($L$2:$L$18, A36)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A36)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K36" s="9" t="b">
+        <f>COUNTIF($R:$R, A36)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="15.5">
-      <c r="A37" s="20" t="s">
+      <c r="R36" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="15.5">
+      <c r="A37" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2560,19 +2895,26 @@
         <v>14</v>
       </c>
       <c r="I37" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A37)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J37" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A37)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N37" t="s">
+        <f>COUNTIF($L$2:$L$18, A37)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J37" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A37)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K37" s="9" t="b">
+        <f>COUNTIF($R:$R, A37)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="15.5">
-      <c r="A38" s="21" t="s">
+      <c r="R37" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15.5">
+      <c r="A38" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2597,19 +2939,26 @@
         <v>14</v>
       </c>
       <c r="I38" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A38)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A38)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
+        <f>COUNTIF($L$2:$L$18, A38)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A38)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="9" t="b">
+        <f>COUNTIF($R:$R, A38)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="15.5">
-      <c r="A39" s="20" t="s">
+      <c r="R38" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="15.5">
+      <c r="A39" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2634,19 +2983,26 @@
         <v>14</v>
       </c>
       <c r="I39" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A39)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A39)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N39" t="s">
+        <f>COUNTIF($L$2:$L$18, A39)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A39)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K39" s="9" t="b">
+        <f>COUNTIF($R:$R, A39)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O39" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="15.5">
-      <c r="A40" s="20" t="s">
+      <c r="R39" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15.5">
+      <c r="A40" s="17" t="s">
         <v>66</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -2671,19 +3027,26 @@
         <v>14</v>
       </c>
       <c r="I40" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A40)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A40)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N40" t="s">
+        <f>COUNTIF($L$2:$L$18, A40)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A40)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K40" s="9" t="b">
+        <f>COUNTIF($R:$R, A40)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="15.5">
-      <c r="A41" s="20" t="s">
+      <c r="R40" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.5">
+      <c r="A41" s="17" t="s">
         <v>67</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -2708,19 +3071,26 @@
         <v>14</v>
       </c>
       <c r="I41" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A41)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A41)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N41" t="s">
+        <f>COUNTIF($L$2:$L$18, A41)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A41)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K41" s="9" t="b">
+        <f>COUNTIF($R:$R, A41)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="15.5">
-      <c r="A42" s="20" t="s">
+      <c r="R41" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15.5">
+      <c r="A42" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -2745,19 +3115,26 @@
         <v>14</v>
       </c>
       <c r="I42" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A42)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A42)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N42" t="s">
+        <f>COUNTIF($L$2:$L$18, A42)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A42)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K42" s="9" t="b">
+        <f>COUNTIF($R:$R, A42)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="15.5">
-      <c r="A43" s="20" t="s">
+      <c r="R42" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15.5">
+      <c r="A43" s="17" t="s">
         <v>69</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -2782,19 +3159,26 @@
         <v>14</v>
       </c>
       <c r="I43" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A43)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A43)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N43" t="s">
+        <f>COUNTIF($L$2:$L$18, A43)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A43)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K43" s="9" t="b">
+        <f>COUNTIF($R:$R, A43)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="15.5">
-      <c r="A44" s="20" t="s">
+      <c r="R43" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15.5">
+      <c r="A44" s="17" t="s">
         <v>70</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -2819,19 +3203,26 @@
         <v>14</v>
       </c>
       <c r="I44" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A44)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A44)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
+        <f>COUNTIF($L$2:$L$18, A44)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A44)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="9" t="b">
+        <f>COUNTIF($R:$R, A44)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="15.5">
-      <c r="A45" s="20" t="s">
+      <c r="R44" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="15.5">
+      <c r="A45" s="17" t="s">
         <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2856,19 +3247,26 @@
         <v>14</v>
       </c>
       <c r="I45" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A45)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A45)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N45" t="s">
+        <f>COUNTIF($L$2:$L$18, A45)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A45)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K45" s="9" t="b">
+        <f>COUNTIF($R:$R, A45)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="15.5">
-      <c r="A46" s="20" t="s">
+      <c r="R45" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15.5">
+      <c r="A46" s="17" t="s">
         <v>72</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2893,19 +3291,26 @@
         <v>14</v>
       </c>
       <c r="I46" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A46)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A46)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N46" t="s">
+        <f>COUNTIF($L$2:$L$18, A46)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A46)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K46" s="9" t="b">
+        <f>COUNTIF($R:$R, A46)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="15.5">
-      <c r="A47" s="20" t="s">
+      <c r="R46" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15.5">
+      <c r="A47" s="17" t="s">
         <v>73</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -2930,19 +3335,26 @@
         <v>14</v>
       </c>
       <c r="I47" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A47)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J47" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A47)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N47" t="s">
+        <f>COUNTIF($L$2:$L$18, A47)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J47" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A47)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K47" s="9" t="b">
+        <f>COUNTIF($R:$R, A47)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="15.5">
-      <c r="A48" s="20" t="s">
+      <c r="R47" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15.5">
+      <c r="A48" s="17" t="s">
         <v>74</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -2967,19 +3379,26 @@
         <v>14</v>
       </c>
       <c r="I48" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A48)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A48)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N48" t="s">
+        <f>COUNTIF($L$2:$L$18, A48)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A48)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K48" s="9" t="b">
+        <f>COUNTIF($R:$R, A48)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O48" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="15.5">
-      <c r="A49" s="20" t="s">
+      <c r="R48" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15.5">
+      <c r="A49" s="17" t="s">
         <v>75</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -3004,19 +3423,26 @@
         <v>14</v>
       </c>
       <c r="I49" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A49)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A49)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N49" t="s">
+        <f>COUNTIF($L$2:$L$18, A49)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A49)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K49" s="9" t="b">
+        <f>COUNTIF($R:$R, A49)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="15.5">
-      <c r="A50" s="20" t="s">
+      <c r="R49" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15.5">
+      <c r="A50" s="17" t="s">
         <v>77</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -3041,19 +3467,26 @@
         <v>14</v>
       </c>
       <c r="I50" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A50)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A50)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N50" t="s">
+        <f>COUNTIF($L$2:$L$18, A50)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A50)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K50" s="9" t="b">
+        <f>COUNTIF($R:$R, A50)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="15.5">
-      <c r="A51" s="20" t="s">
+      <c r="R50" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15.5">
+      <c r="A51" s="17" t="s">
         <v>78</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -3078,19 +3511,26 @@
         <v>14</v>
       </c>
       <c r="I51" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A51)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A51)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N51" t="s">
+        <f>COUNTIF($L$2:$L$18, A51)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A51)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K51" s="9" t="b">
+        <f>COUNTIF($R:$R, A51)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="15.5">
-      <c r="A52" s="20" t="s">
+      <c r="R51" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15.5">
+      <c r="A52" s="17" t="s">
         <v>79</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -3115,19 +3555,26 @@
         <v>14</v>
       </c>
       <c r="I52" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A52)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A52)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N52" t="s">
+        <f>COUNTIF($L$2:$L$18, A52)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A52)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K52" s="9" t="b">
+        <f>COUNTIF($R:$R, A52)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="15.5">
-      <c r="A53" s="20" t="s">
+      <c r="R52" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="15.5">
+      <c r="A53" s="17" t="s">
         <v>80</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -3152,19 +3599,26 @@
         <v>14</v>
       </c>
       <c r="I53" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A53)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A53)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N53" t="s">
+        <f>COUNTIF($L$2:$L$18, A53)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A53)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K53" s="9" t="b">
+        <f>COUNTIF($R:$R, A53)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="15.5">
-      <c r="A54" s="20" t="s">
+      <c r="R53" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15.5">
+      <c r="A54" s="17" t="s">
         <v>81</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -3189,19 +3643,26 @@
         <v>14</v>
       </c>
       <c r="I54" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A54)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A54)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N54" t="s">
+        <f>COUNTIF($L$2:$L$18, A54)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A54)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="9" t="b">
+        <f>COUNTIF($R:$R, A54)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="15.5">
-      <c r="A55" s="21" t="s">
+      <c r="R54" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="15.5">
+      <c r="A55" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -3226,19 +3687,26 @@
         <v>14</v>
       </c>
       <c r="I55" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A55)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A55)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N55" t="s">
+        <f>COUNTIF($L$2:$L$18, A55)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A55)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="9" t="b">
+        <f>COUNTIF($R:$R, A55)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="15.5">
-      <c r="A56" s="20" t="s">
+      <c r="R55" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="15.5">
+      <c r="A56" s="17" t="s">
         <v>83</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -3263,19 +3731,26 @@
         <v>14</v>
       </c>
       <c r="I56" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A56)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A56)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N56" t="s">
+        <f>COUNTIF($L$2:$L$18, A56)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A56)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K56" s="9" t="b">
+        <f>COUNTIF($R:$R, A56)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="15.5">
-      <c r="A57" s="20" t="s">
+      <c r="R56" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="15.5">
+      <c r="A57" s="17" t="s">
         <v>84</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -3300,19 +3775,26 @@
         <v>14</v>
       </c>
       <c r="I57" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A57)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J57" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A57)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N57" t="s">
+        <f>COUNTIF($L$2:$L$18, A57)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A57)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K57" s="9" t="b">
+        <f>COUNTIF($R:$R, A57)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="15.5">
-      <c r="A58" s="20" t="s">
+      <c r="R57" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="15.5">
+      <c r="A58" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -3337,19 +3819,26 @@
         <v>14</v>
       </c>
       <c r="I58" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A58)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A58)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N58" t="s">
+        <f>COUNTIF($L$2:$L$18, A58)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A58)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K58" s="9" t="b">
+        <f>COUNTIF($R:$R, A58)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="15.5">
-      <c r="A59" s="20" t="s">
+      <c r="R58" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="15.5">
+      <c r="A59" s="17" t="s">
         <v>86</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3374,19 +3863,26 @@
         <v>14</v>
       </c>
       <c r="I59" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A59)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J59" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A59)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N59" t="s">
+        <f>COUNTIF($L$2:$L$18, A59)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J59" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A59)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K59" s="9" t="b">
+        <f>COUNTIF($R:$R, A59)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="15.5">
-      <c r="A60" s="20" t="s">
+      <c r="R59" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="15.5">
+      <c r="A60" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -3411,19 +3907,26 @@
         <v>14</v>
       </c>
       <c r="I60" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A60)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J60" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A60)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N60" t="s">
+        <f>COUNTIF($L$2:$L$18, A60)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A60)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K60" s="9" t="b">
+        <f>COUNTIF($R:$R, A60)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O60" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="15.5">
-      <c r="A61" s="20" t="s">
+      <c r="R60" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15.5">
+      <c r="A61" s="17" t="s">
         <v>88</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -3448,19 +3951,26 @@
         <v>14</v>
       </c>
       <c r="I61" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A61)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J61" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A61)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N61" t="s">
+        <f>COUNTIF($L$2:$L$18, A61)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A61)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K61" s="9" t="b">
+        <f>COUNTIF($R:$R, A61)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="15.5">
-      <c r="A62" s="20" t="s">
+      <c r="R61" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15.5">
+      <c r="A62" s="17" t="s">
         <v>89</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -3485,19 +3995,26 @@
         <v>14</v>
       </c>
       <c r="I62" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A62)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J62" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A62)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N62" t="s">
+        <f>COUNTIF($L$2:$L$18, A62)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J62" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A62)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K62" s="9" t="b">
+        <f>COUNTIF($R:$R, A62)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O62" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="15.5">
-      <c r="A63" s="20" t="s">
+      <c r="R62" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.5">
+      <c r="A63" s="17" t="s">
         <v>90</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -3522,19 +4039,26 @@
         <v>14</v>
       </c>
       <c r="I63" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A63)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A63)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N63" t="s">
+        <f>COUNTIF($L$2:$L$18, A63)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A63)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K63" s="9" t="b">
+        <f>COUNTIF($R:$R, A63)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15.5">
-      <c r="A64" s="20" t="s">
+      <c r="R63" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="15.5">
+      <c r="A64" s="17" t="s">
         <v>92</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -3559,19 +4083,26 @@
         <v>14</v>
       </c>
       <c r="I64" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A64)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A64)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N64" t="s">
+        <f>COUNTIF($L$2:$L$18, A64)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A64)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K64" s="9" t="b">
+        <f>COUNTIF($R:$R, A64)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="15.5">
-      <c r="A65" s="20" t="s">
+      <c r="R64" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="15.5">
+      <c r="A65" s="17" t="s">
         <v>93</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -3596,19 +4127,26 @@
         <v>94</v>
       </c>
       <c r="I65" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A65)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J65" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A65)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N65" t="s">
+        <f>COUNTIF($L$2:$L$18, A65)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J65" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A65)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K65" s="9" t="b">
+        <f>COUNTIF($R:$R, A65)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="15.5">
-      <c r="A66" s="21" t="s">
+      <c r="R65" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="15.5">
+      <c r="A66" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -3633,19 +4171,26 @@
         <v>14</v>
       </c>
       <c r="I66" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A66)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A66)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N66" t="s">
+        <f>COUNTIF($L$2:$L$18, A66)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A66)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="9" t="b">
+        <f>COUNTIF($R:$R, A66)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15.5">
-      <c r="A67" s="20" t="s">
+      <c r="R66" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="15.5">
+      <c r="A67" s="17" t="s">
         <v>96</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -3670,19 +4215,26 @@
         <v>14</v>
       </c>
       <c r="I67" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A67)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A67)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N67" t="s">
+        <f>COUNTIF($L$2:$L$18, A67)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A67)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K67" s="9" t="b">
+        <f>COUNTIF($R:$R, A67)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="15.5">
-      <c r="A68" s="20" t="s">
+      <c r="R67" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="15.5">
+      <c r="A68" s="17" t="s">
         <v>97</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -3707,19 +4259,26 @@
         <v>14</v>
       </c>
       <c r="I68" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A68)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J68" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A68)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N68" t="s">
+        <f>COUNTIF($L$2:$L$18, A68)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A68)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K68" s="9" t="b">
+        <f>COUNTIF($R:$R, A68)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="15.5">
-      <c r="A69" s="20" t="s">
+      <c r="R68" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="15.5">
+      <c r="A69" s="17" t="s">
         <v>98</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -3744,19 +4303,26 @@
         <v>14</v>
       </c>
       <c r="I69" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A69)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J69" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A69)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N69" t="s">
+        <f>COUNTIF($L$2:$L$18, A69)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A69)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K69" s="9" t="b">
+        <f>COUNTIF($R:$R, A69)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="15.5">
-      <c r="A70" s="20" t="s">
+      <c r="R69" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="15.5">
+      <c r="A70" s="17" t="s">
         <v>99</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -3781,19 +4347,26 @@
         <v>14</v>
       </c>
       <c r="I70" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A70)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A70)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N70" t="s">
+        <f>COUNTIF($L$2:$L$18, A70)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A70)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K70" s="9" t="b">
+        <f>COUNTIF($R:$R, A70)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="15.5">
-      <c r="A71" s="20" t="s">
+      <c r="R70" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="15.5">
+      <c r="A71" s="17" t="s">
         <v>100</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -3818,19 +4391,26 @@
         <v>14</v>
       </c>
       <c r="I71" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A71)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J71" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A71)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N71" t="s">
+        <f>COUNTIF($L$2:$L$18, A71)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J71" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A71)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K71" s="9" t="b">
+        <f>COUNTIF($R:$R, A71)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="15.5">
-      <c r="A72" s="20" t="s">
+      <c r="R71" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="15.5">
+      <c r="A72" s="17" t="s">
         <v>101</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -3855,19 +4435,26 @@
         <v>14</v>
       </c>
       <c r="I72" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A72)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J72" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A72)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N72" t="s">
+        <f>COUNTIF($L$2:$L$18, A72)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J72" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A72)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K72" s="9" t="b">
+        <f>COUNTIF($R:$R, A72)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="15.5">
-      <c r="A73" s="20" t="s">
+      <c r="R72" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="15.5">
+      <c r="A73" s="17" t="s">
         <v>102</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -3892,19 +4479,26 @@
         <v>14</v>
       </c>
       <c r="I73" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A73)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A73)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N73" t="s">
+        <f>COUNTIF($L$2:$L$18, A73)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A73)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K73" s="9" t="b">
+        <f>COUNTIF($R:$R, A73)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="15.5">
-      <c r="A74" s="20" t="s">
+      <c r="R73" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="15.5">
+      <c r="A74" s="17" t="s">
         <v>103</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -3929,19 +4523,26 @@
         <v>14</v>
       </c>
       <c r="I74" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A74)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J74" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A74)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N74" t="s">
+        <f>COUNTIF($L$2:$L$18, A74)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A74)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K74" s="9" t="b">
+        <f>COUNTIF($R:$R, A74)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="16" thickBot="1">
-      <c r="A75" s="22" t="s">
+      <c r="R74" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="16" thickBot="1">
+      <c r="A75" s="18" t="s">
         <v>104</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -3966,19 +4567,26 @@
         <v>14</v>
       </c>
       <c r="I75" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A75)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A75)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N75" t="s">
+        <f>COUNTIF($L$2:$L$18, A75)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A75)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K75" s="9" t="b">
+        <f>COUNTIF($R:$R, A75)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="16.5" thickTop="1">
-      <c r="A76" s="20" t="s">
+      <c r="R75" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="16.5" thickTop="1">
+      <c r="A76" s="17" t="s">
         <v>105</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -4003,19 +4611,26 @@
         <v>14</v>
       </c>
       <c r="I76" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A76)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J76" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A76)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N76" t="s">
+        <f>COUNTIF($L$2:$L$18, A76)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A76)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K76" s="9" t="b">
+        <f>COUNTIF($R:$R, A76)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="16">
-      <c r="A77" s="20" t="s">
+      <c r="R76" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="16">
+      <c r="A77" s="17" t="s">
         <v>107</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -4040,19 +4655,26 @@
         <v>14</v>
       </c>
       <c r="I77" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A77)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J77" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A77)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N77" t="s">
+        <f>COUNTIF($L$2:$L$18, A77)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J77" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A77)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K77" s="9" t="b">
+        <f>COUNTIF($R:$R, A77)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O77" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="16">
-      <c r="A78" s="20" t="s">
+      <c r="R77" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="16">
+      <c r="A78" s="17" t="s">
         <v>109</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -4077,19 +4699,26 @@
         <v>14</v>
       </c>
       <c r="I78" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A78)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A78)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N78" t="s">
+        <f>COUNTIF($L$2:$L$18, A78)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A78)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K78" s="9" t="b">
+        <f>COUNTIF($R:$R, A78)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="16">
-      <c r="A79" s="20" t="s">
+      <c r="R78" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="16">
+      <c r="A79" s="17" t="s">
         <v>110</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -4106,19 +4735,26 @@
         <v>14</v>
       </c>
       <c r="I79" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A79)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J79" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A79)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N79" t="s">
+        <f>COUNTIF($L$2:$L$18, A79)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J79" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A79)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K79" s="9" t="b">
+        <f>COUNTIF($R:$R, A79)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O79" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="16">
-      <c r="A80" s="20" t="s">
+      <c r="R79" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="16">
+      <c r="A80" s="17" t="s">
         <v>111</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -4143,19 +4779,26 @@
         <v>14</v>
       </c>
       <c r="I80" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A80)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J80" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A80)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N80" t="s">
+        <f>COUNTIF($L$2:$L$18, A80)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J80" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A80)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K80" s="9" t="b">
+        <f>COUNTIF($R:$R, A80)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="16">
-      <c r="A81" s="20" t="s">
+      <c r="R80" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="16">
+      <c r="A81" s="17" t="s">
         <v>114</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -4168,19 +4811,26 @@
       <c r="G81" s="1"/>
       <c r="H81" s="5"/>
       <c r="I81" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A81)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A81)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N81" t="s">
+        <f>COUNTIF($L$2:$L$18, A81)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A81)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="9" t="b">
+        <f>COUNTIF($R:$R, A81)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O81" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="16">
-      <c r="A82" s="20" t="s">
+      <c r="R81" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="16">
+      <c r="A82" s="17" t="s">
         <v>115</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -4197,19 +4847,26 @@
         <v>94</v>
       </c>
       <c r="I82" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A82)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A82)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N82" t="s">
+        <f>COUNTIF($L$2:$L$18, A82)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A82)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K82" s="9" t="b">
+        <f>COUNTIF($R:$R, A82)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O82" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="16">
-      <c r="A83" s="20" t="s">
+      <c r="R82" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="16">
+      <c r="A83" s="17" t="s">
         <v>116</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -4234,19 +4891,26 @@
         <v>14</v>
       </c>
       <c r="I83" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A83)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J83" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A83)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N83" t="s">
+        <f>COUNTIF($L$2:$L$18, A83)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J83" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A83)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K83" s="9" t="b">
+        <f>COUNTIF($R:$R, A83)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O83" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="16">
-      <c r="A84" s="20" t="s">
+      <c r="R83" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="16">
+      <c r="A84" s="17" t="s">
         <v>117</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -4271,19 +4935,26 @@
         <v>14</v>
       </c>
       <c r="I84" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A84)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A84)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N84" t="s">
+        <f>COUNTIF($L$2:$L$18, A84)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A84)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K84" s="9" t="b">
+        <f>COUNTIF($R:$R, A84)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O84" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="16">
-      <c r="A85" s="20" t="s">
+      <c r="R84" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="16">
+      <c r="A85" s="17" t="s">
         <v>118</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -4308,19 +4979,26 @@
         <v>14</v>
       </c>
       <c r="I85" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A85)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A85)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N85" t="s">
+        <f>COUNTIF($L$2:$L$18, A85)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A85)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K85" s="9" t="b">
+        <f>COUNTIF($R:$R, A85)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O85" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="16">
-      <c r="A86" s="20" t="s">
+      <c r="R85" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="16">
+      <c r="A86" s="17" t="s">
         <v>120</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -4345,19 +5023,26 @@
         <v>14</v>
       </c>
       <c r="I86" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A86)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J86" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A86)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N86" t="s">
+        <f>COUNTIF($L$2:$L$18, A86)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J86" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A86)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K86" s="9" t="b">
+        <f>COUNTIF($R:$R, A86)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="16">
-      <c r="A87" s="20" t="s">
+      <c r="R86" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="16">
+      <c r="A87" s="17" t="s">
         <v>121</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -4382,19 +5067,26 @@
         <v>14</v>
       </c>
       <c r="I87" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A87)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J87" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A87)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N87" t="s">
+        <f>COUNTIF($L$2:$L$18, A87)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J87" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A87)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K87" s="9" t="b">
+        <f>COUNTIF($R:$R, A87)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O87" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="16">
-      <c r="A88" s="20" t="s">
+      <c r="R87" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="16">
+      <c r="A88" s="17" t="s">
         <v>122</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -4419,19 +5111,26 @@
         <v>14</v>
       </c>
       <c r="I88" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A88)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J88" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A88)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N88" t="s">
+        <f>COUNTIF($L$2:$L$18, A88)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J88" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A88)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K88" s="9" t="b">
+        <f>COUNTIF($R:$R, A88)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O88" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" ht="16">
-      <c r="A89" s="20" t="s">
+      <c r="R88" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="16">
+      <c r="A89" s="17" t="s">
         <v>124</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -4456,19 +5155,26 @@
         <v>14</v>
       </c>
       <c r="I89" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A89)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J89" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A89)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N89" t="s">
+        <f>COUNTIF($L$2:$L$18, A89)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J89" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A89)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K89" s="9" t="b">
+        <f>COUNTIF($R:$R, A89)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" ht="16">
-      <c r="A90" s="20" t="s">
+      <c r="R89" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="16">
+      <c r="A90" s="17" t="s">
         <v>126</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -4493,19 +5199,26 @@
         <v>14</v>
       </c>
       <c r="I90" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A90)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J90" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A90)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N90" t="s">
+        <f>COUNTIF($L$2:$L$18, A90)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J90" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A90)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K90" s="9" t="b">
+        <f>COUNTIF($R:$R, A90)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O90" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" ht="16">
-      <c r="A91" s="20" t="s">
+      <c r="R90" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="16">
+      <c r="A91" s="17" t="s">
         <v>127</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -4530,19 +5243,26 @@
         <v>14</v>
       </c>
       <c r="I91" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A91)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J91" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A91)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N91" t="s">
+        <f>COUNTIF($L$2:$L$18, A91)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A91)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K91" s="9" t="b">
+        <f>COUNTIF($R:$R, A91)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" ht="16">
-      <c r="A92" s="20" t="s">
+      <c r="R91" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="16">
+      <c r="A92" s="17" t="s">
         <v>128</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -4567,19 +5287,26 @@
         <v>14</v>
       </c>
       <c r="I92" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A92)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J92" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A92)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N92" t="s">
+        <f>COUNTIF($L$2:$L$18, A92)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J92" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A92)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K92" s="9" t="b">
+        <f>COUNTIF($R:$R, A92)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="O92" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" ht="16">
-      <c r="A93" s="20" t="s">
+      <c r="R92" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="16">
+      <c r="A93" s="17" t="s">
         <v>129</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -4604,19 +5331,26 @@
         <v>14</v>
       </c>
       <c r="I93" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A93)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J93" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A93)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N93" t="s">
+        <f>COUNTIF($L$2:$L$18, A93)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J93" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A93)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K93" s="9" t="b">
+        <f>COUNTIF($R:$R, A93)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O93" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" ht="16">
-      <c r="A94" s="20" t="s">
+      <c r="R93" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="16">
+      <c r="A94" s="17" t="s">
         <v>131</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -4641,19 +5375,26 @@
         <v>14</v>
       </c>
       <c r="I94" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A94)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A94)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N94" t="s">
+        <f>COUNTIF($L$2:$L$18, A94)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A94)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K94" s="9" t="b">
+        <f>COUNTIF($R:$R, A94)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" ht="16">
-      <c r="A95" s="20" t="s">
+      <c r="R94" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="16">
+      <c r="A95" s="17" t="s">
         <v>133</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -4678,19 +5419,26 @@
         <v>14</v>
       </c>
       <c r="I95" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A95)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J95" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A95)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="N95" t="s">
+        <f>COUNTIF($L$2:$L$18, A95)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A95)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K95" s="9" t="b">
+        <f>COUNTIF($R:$R, A95)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" ht="16">
-      <c r="A96" s="20" t="s">
+      <c r="R95" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="16">
+      <c r="A96" s="17" t="s">
         <v>134</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -4715,16 +5463,20 @@
         <v>14</v>
       </c>
       <c r="I96" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A96)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J96" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A96)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="16">
-      <c r="A97" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A96)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J96" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A96)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K96" s="9" t="b">
+        <f>COUNTIF($R:$R, A96)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="16">
+      <c r="A97" s="17" t="s">
         <v>135</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -4749,16 +5501,20 @@
         <v>14</v>
       </c>
       <c r="I97" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A97)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A97)&gt;0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="16">
-      <c r="A98" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A97)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J97" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A97)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K97" s="9" t="b">
+        <f>COUNTIF($R:$R, A97)&gt;0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="16">
+      <c r="A98" s="17" t="s">
         <v>136</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -4783,16 +5539,20 @@
         <v>14</v>
       </c>
       <c r="I98" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A98)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A98)&gt;0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="16">
-      <c r="A99" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A98)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J98" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A98)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K98" s="9" t="b">
+        <f>COUNTIF($R:$R, A98)&gt;0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="16">
+      <c r="A99" s="17" t="s">
         <v>137</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -4817,16 +5577,20 @@
         <v>14</v>
       </c>
       <c r="I99" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A99)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J99" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A99)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="16">
-      <c r="A100" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A99)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A99)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K99" s="9" t="b">
+        <f>COUNTIF($R:$R, A99)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="16">
+      <c r="A100" s="17" t="s">
         <v>138</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -4847,16 +5611,20 @@
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A100)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A100)&gt;0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="16">
-      <c r="A101" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A100)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J100" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A100)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K100" s="9" t="b">
+        <f>COUNTIF($R:$R, A100)&gt;0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="16">
+      <c r="A101" s="17" t="s">
         <v>139</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -4881,16 +5649,20 @@
         <v>14</v>
       </c>
       <c r="I101" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A101)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J101" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A101)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="16">
-      <c r="A102" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A101)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J101" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A101)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K101" s="9" t="b">
+        <f>COUNTIF($R:$R, A101)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="16">
+      <c r="A102" s="17" t="s">
         <v>141</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -4915,16 +5687,20 @@
         <v>14</v>
       </c>
       <c r="I102" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A102)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A102)&gt;0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="16">
-      <c r="A103" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A102)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J102" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A102)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K102" s="9" t="b">
+        <f>COUNTIF($R:$R, A102)&gt;0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="16">
+      <c r="A103" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -4949,16 +5725,20 @@
         <v>14</v>
       </c>
       <c r="I103" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A103)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J103" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A103)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="16">
-      <c r="A104" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A103)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J103" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A103)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K103" s="9" t="b">
+        <f>COUNTIF($R:$R, A103)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="16">
+      <c r="A104" s="17" t="s">
         <v>143</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -4981,16 +5761,20 @@
         <v>14</v>
       </c>
       <c r="I104" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A104)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J104" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A104)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="16">
-      <c r="A105" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A104)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J104" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A104)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K104" s="9" t="b">
+        <f>COUNTIF($R:$R, A104)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="16">
+      <c r="A105" s="17" t="s">
         <v>144</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -5013,16 +5797,20 @@
         <v>14</v>
       </c>
       <c r="I105" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A105)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J105" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A105)&gt;0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="16">
-      <c r="A106" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A105)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J105" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A105)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K105" s="9" t="b">
+        <f>COUNTIF($R:$R, A105)&gt;0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="16">
+      <c r="A106" s="17" t="s">
         <v>145</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -5045,16 +5833,20 @@
         <v>14</v>
       </c>
       <c r="I106" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A106)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J106" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A106)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="16">
-      <c r="A107" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A106)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J106" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A106)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K106" s="9" t="b">
+        <f>COUNTIF($R:$R, A106)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="16">
+      <c r="A107" s="17" t="s">
         <v>146</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -5077,16 +5869,20 @@
         <v>14</v>
       </c>
       <c r="I107" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A107)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J107" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A107)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="16">
-      <c r="A108" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A107)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A107)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K107" s="9" t="b">
+        <f>COUNTIF($R:$R, A107)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="16">
+      <c r="A108" s="17" t="s">
         <v>147</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -5109,16 +5905,20 @@
         <v>14</v>
       </c>
       <c r="I108" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A108)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J108" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A108)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="16">
-      <c r="A109" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A108)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J108" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A108)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K108" s="9" t="b">
+        <f>COUNTIF($R:$R, A108)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="16">
+      <c r="A109" s="17" t="s">
         <v>148</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -5141,16 +5941,20 @@
         <v>14</v>
       </c>
       <c r="I109" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A109)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J109" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A109)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="16">
-      <c r="A110" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A109)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J109" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A109)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K109" s="9" t="b">
+        <f>COUNTIF($R:$R, A109)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="16">
+      <c r="A110" s="17" t="s">
         <v>149</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -5173,16 +5977,20 @@
         <v>14</v>
       </c>
       <c r="I110" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A110)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J110" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A110)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="16">
-      <c r="A111" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A110)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J110" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A110)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K110" s="9" t="b">
+        <f>COUNTIF($R:$R, A110)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="16">
+      <c r="A111" s="17" t="s">
         <v>150</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -5205,16 +6013,20 @@
         <v>14</v>
       </c>
       <c r="I111" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A111)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J111" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A111)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="16">
-      <c r="A112" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A111)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J111" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A111)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K111" s="9" t="b">
+        <f>COUNTIF($R:$R, A111)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="16">
+      <c r="A112" s="17" t="s">
         <v>151</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -5239,16 +6051,20 @@
         <v>94</v>
       </c>
       <c r="I112" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A112)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J112" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A112)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="16">
-      <c r="A113" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A112)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J112" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A112)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K112" s="9" t="b">
+        <f>COUNTIF($R:$R, A112)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="16">
+      <c r="A113" s="17" t="s">
         <v>152</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -5261,16 +6077,20 @@
       <c r="G113" s="1"/>
       <c r="H113" s="5"/>
       <c r="I113" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A113)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J113" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A113)&gt;0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="16">
-      <c r="A114" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A113)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A113)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K113" s="9" t="b">
+        <f>COUNTIF($R:$R, A113)&gt;0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="16">
+      <c r="A114" s="17" t="s">
         <v>153</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -5293,16 +6113,20 @@
         <v>14</v>
       </c>
       <c r="I114" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A114)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J114" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A114)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="16">
-      <c r="A115" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A114)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A114)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K114" s="9" t="b">
+        <f>COUNTIF($R:$R, A114)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="16">
+      <c r="A115" s="17" t="s">
         <v>154</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -5325,16 +6149,20 @@
         <v>14</v>
       </c>
       <c r="I115" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A115)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J115" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A115)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="16">
-      <c r="A116" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A115)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J115" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A115)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K115" s="9" t="b">
+        <f>COUNTIF($R:$R, A115)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="16">
+      <c r="A116" s="17" t="s">
         <v>155</v>
       </c>
       <c r="B116" s="7" t="s">
@@ -5357,16 +6185,20 @@
         <v>14</v>
       </c>
       <c r="I116" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A116)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J116" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A116)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="16">
-      <c r="A117" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A116)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J116" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A116)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K116" s="9" t="b">
+        <f>COUNTIF($R:$R, A116)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="16">
+      <c r="A117" s="17" t="s">
         <v>156</v>
       </c>
       <c r="B117" s="7" t="s">
@@ -5389,16 +6221,20 @@
         <v>14</v>
       </c>
       <c r="I117" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A117)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J117" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A117)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="16">
-      <c r="A118" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A117)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J117" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A117)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K117" s="9" t="b">
+        <f>COUNTIF($R:$R, A117)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="16">
+      <c r="A118" s="17" t="s">
         <v>157</v>
       </c>
       <c r="B118" s="7" t="s">
@@ -5421,16 +6257,20 @@
         <v>14</v>
       </c>
       <c r="I118" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A118)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J118" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A118)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="16">
-      <c r="A119" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A118)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J118" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A118)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K118" s="9" t="b">
+        <f>COUNTIF($R:$R, A118)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="16">
+      <c r="A119" s="17" t="s">
         <v>158</v>
       </c>
       <c r="B119" s="7" t="s">
@@ -5453,16 +6293,20 @@
         <v>14</v>
       </c>
       <c r="I119" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A119)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J119" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A119)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="16">
-      <c r="A120" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A119)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J119" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A119)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K119" s="9" t="b">
+        <f>COUNTIF($R:$R, A119)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="16">
+      <c r="A120" s="17" t="s">
         <v>159</v>
       </c>
       <c r="B120" s="7" t="s">
@@ -5485,16 +6329,20 @@
         <v>14</v>
       </c>
       <c r="I120" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A120)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J120" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A120)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="16">
-      <c r="A121" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A120)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J120" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A120)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K120" s="9" t="b">
+        <f>COUNTIF($R:$R, A120)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="16">
+      <c r="A121" s="17" t="s">
         <v>160</v>
       </c>
       <c r="B121" s="7" t="s">
@@ -5517,16 +6365,20 @@
         <v>94</v>
       </c>
       <c r="I121" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A121)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J121" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A121)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="16">
-      <c r="A122" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A121)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J121" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A121)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K121" s="9" t="b">
+        <f>COUNTIF($R:$R, A121)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="16">
+      <c r="A122" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B122" s="7" t="s">
@@ -5549,16 +6401,20 @@
         <v>14</v>
       </c>
       <c r="I122" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A122)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J122" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A122)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="16">
-      <c r="A123" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A122)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J122" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A122)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K122" s="9" t="b">
+        <f>COUNTIF($R:$R, A122)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="16">
+      <c r="A123" s="17" t="s">
         <v>162</v>
       </c>
       <c r="B123" s="7" t="s">
@@ -5581,16 +6437,20 @@
         <v>14</v>
       </c>
       <c r="I123" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A123)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J123" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A123)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="16">
-      <c r="A124" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A123)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J123" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A123)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K123" s="9" t="b">
+        <f>COUNTIF($R:$R, A123)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="16">
+      <c r="A124" s="17" t="s">
         <v>163</v>
       </c>
       <c r="B124" s="7" t="s">
@@ -5613,16 +6473,20 @@
         <v>14</v>
       </c>
       <c r="I124" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A124)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J124" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A124)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="16">
-      <c r="A125" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A124)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J124" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A124)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K124" s="9" t="b">
+        <f>COUNTIF($R:$R, A124)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="16">
+      <c r="A125" s="17" t="s">
         <v>164</v>
       </c>
       <c r="B125" s="7" t="s">
@@ -5645,16 +6509,20 @@
         <v>14</v>
       </c>
       <c r="I125" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A125)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J125" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A125)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="16">
-      <c r="A126" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A125)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J125" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A125)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K125" s="9" t="b">
+        <f>COUNTIF($R:$R, A125)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="16">
+      <c r="A126" s="17" t="s">
         <v>165</v>
       </c>
       <c r="B126" s="7" t="s">
@@ -5677,16 +6545,20 @@
         <v>14</v>
       </c>
       <c r="I126" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A126)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J126" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A126)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="16">
-      <c r="A127" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A126)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J126" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A126)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K126" s="9" t="b">
+        <f>COUNTIF($R:$R, A126)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="16">
+      <c r="A127" s="17" t="s">
         <v>166</v>
       </c>
       <c r="B127" s="7" t="s">
@@ -5709,16 +6581,20 @@
         <v>14</v>
       </c>
       <c r="I127" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A127)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J127" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A127)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="16">
-      <c r="A128" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A127)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J127" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A127)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K127" s="9" t="b">
+        <f>COUNTIF($R:$R, A127)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="16">
+      <c r="A128" s="17" t="s">
         <v>167</v>
       </c>
       <c r="B128" s="7" t="s">
@@ -5741,16 +6617,20 @@
         <v>14</v>
       </c>
       <c r="I128" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A128)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J128" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A128)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="16">
-      <c r="A129" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A128)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J128" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A128)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K128" s="9" t="b">
+        <f>COUNTIF($R:$R, A128)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="16">
+      <c r="A129" s="17" t="s">
         <v>168</v>
       </c>
       <c r="B129" s="7" t="s">
@@ -5773,16 +6653,20 @@
         <v>14</v>
       </c>
       <c r="I129" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A129)&gt;0</f>
-        <v>1</v>
-      </c>
-      <c r="J129" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A129)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="16">
-      <c r="A130" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A129)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J129" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A129)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K129" s="9" t="b">
+        <f>COUNTIF($R:$R, A129)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="16">
+      <c r="A130" s="17" t="s">
         <v>169</v>
       </c>
       <c r="B130" s="7" t="s">
@@ -5805,16 +6689,20 @@
         <v>14</v>
       </c>
       <c r="I130" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A130)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J130" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A130)&gt;0</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="16">
-      <c r="A131" s="20" t="s">
+        <f>COUNTIF($L$2:$L$18, A130)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J130" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A130)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K130" s="9" t="b">
+        <f>COUNTIF($R:$R, A130)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="16">
+      <c r="A131" s="17" t="s">
         <v>170</v>
       </c>
       <c r="B131" s="7" t="s">
@@ -5837,12 +6725,51 @@
         <v>14</v>
       </c>
       <c r="I131" s="2" t="b">
-        <f>COUNTIF($K$2:$K$18, A131)&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="J131" s="13" t="b">
-        <f>COUNTIF($N$2:$N$95, A131)&gt;0</f>
-        <v>1</v>
+        <f>COUNTIF($L$2:$L$18, A131)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="J131" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A131)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="K131" s="9" t="b">
+        <f>COUNTIF($R:$R, A131)&gt;0</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="16">
+      <c r="A132" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" s="2">
+        <v>30</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" s="2" t="b">
+        <f>COUNTIF($L$2:$L$19, A132)&gt;0</f>
+        <v>1</v>
+      </c>
+      <c r="J132" s="19" t="b">
+        <f>COUNTIF($O$2:$O$95, A132)&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="K132" s="9" t="b">
+        <f>COUNTIF($R:$R, A132)&gt;0</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
